--- a/請GPT產生初版教材.xlsx
+++ b/請GPT產生初版教材.xlsx
@@ -31,7 +31,7 @@
 1. 什麼是資料探勘?
 2. 為什麼需要資料探勘, 依功能(目的)來分它可以分成那幾類? 並都舉例應用在那些行業上?
 3. 以(2)的分類來說, 資料探勘完成, 最終的outcome是什麼? 大都如何呈現? 有什作用呢?
-4. 實作時, 資料探勘有那些重要的程序呢? 並稍作解釋
+4. 實作時, 資料探勘有那些重要的程序/階段呢? 並稍作解釋
 5. 實作時, 資料探勘牽涉(會運用)到那些資訊技術? 例如常用的資料庫, 程式語言, 套裝裝軟體 (各舉Top 3)
 6. 資料探勘, 會使用到那些重要的演算法, 根據功能(目的), 將這些演算法分門別類, 並稍作說明</t>
     <phoneticPr fontId="1" type="noConversion"/>

--- a/請GPT產生初版教材.xlsx
+++ b/請GPT產生初版教材.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>幫忙產生markdown 格式的教學內容:
 Title : 資料探勘Data Mining的介紹
@@ -34,6 +34,11 @@
 4. 實作時, 資料探勘有那些重要的程序/階段呢? 並稍作解釋
 5. 實作時, 資料探勘牽涉(會運用)到那些資訊技術? 例如常用的資料庫, 程式語言, 套裝裝軟體 (各舉Top 3)
 6. 資料探勘, 會使用到那些重要的演算法, 根據功能(目的), 將這些演算法分門別類, 並稍作說明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">幫忙產生markdown 格式的教學內容:  
+請說明解釋: Data Mining、Machine Learning、AI、Data Science 四者到底有什麼關係？ </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -367,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1"/>
+  <dimension ref="B1:B2"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="157.109375" customWidth="1"/>
@@ -378,6 +383,11 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="2:2" ht="48.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/請GPT產生初版教材.xlsx
+++ b/請GPT產生初版教材.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>幫忙產生markdown 格式的教學內容:
 Title : 資料探勘Data Mining的介紹
@@ -39,6 +39,26 @@
   <si>
     <t xml:space="preserve">幫忙產生markdown 格式的教學內容:  
 請說明解釋: Data Mining、Machine Learning、AI、Data Science 四者到底有什麼關係？ </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">在大二資料探勘, 分群課程上課前, 以下四個問題請各以半頁至一頁的篇幅跟同學說明
+一. 什麼是資料Data 
+從個人日常的札記, 公司紙本的進出貨資料, 公司電子檔Excel上的進出貨資料/人事/打卡資料,
+公司MS SQL 上的資料庫(欄位, Table), 雲端上的資料,
+文字, 影像, 語音, 對話記錄, mp4
+-
+二. 另外, 也說明一下, 
+公司伺服器上安裝MS SQL 資料庫
+與
+架私有雲/公有雲, 其上安裝公司MS SQL 資料庫
+二者本質/架構/管理/user使用上有何差別
+-
+三. 一般企業要架私有雲/公有雲, 是自架好? 或是委外好?
+-
+四. 公司資料上雲端, 就一定要架私有雲/公有雲嗎? Google 或其他ISP有其他更簡便的方式協助企業資料上雲端嗎?
+如果跟Google申請專屬的企業版 Gmail 與雲端硬碟空間, 其上應該只能上傳file也是不能安裝SQL資料庫, 必須架雲對吧?
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -372,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:B2"/>
+  <dimension ref="B1:B4"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="157.109375" customWidth="1"/>
@@ -388,6 +408,11 @@
         <v>1</v>
       </c>
     </row>
+    <row r="4" spans="2:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/請GPT產生初版教材.xlsx
+++ b/請GPT產生初版教材.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>幫忙產生markdown 格式的教學內容:
 Title : 資料探勘Data Mining的介紹
@@ -42,7 +42,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">在大二資料探勘, 分群課程上課前, 以下四個問題請各以半頁至一頁的篇幅跟同學說明
+    <t xml:space="preserve">1. 機器學習主要分成以下幾種常見的類型  ： 
+監督式學習（Supervised Learning） ,非監督式學習（Unsupervised Learning）  ,強化學習（Reinforcement Learning）  
+請簡單說明介紹,及其應用
+2.非監督式學習的三大功能  :分群  , 關聯, 降維
+請簡單說明介紹, 各別常用的演算法, 及更多實際生活中的應用  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+在大二資料探勘, 分群課程上課前, 以下四個問題請各以半頁至一頁的篇幅跟同學說明
 一. 什麼是資料Data 
 從個人日常的札記, 公司紙本的進出貨資料, 公司電子檔Excel上的進出貨資料/人事/打卡資料,
 公司MS SQL 上的資料庫(欄位, Table), 雲端上的資料,
@@ -392,23 +401,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:B4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="157.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="243" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="243" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>1</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:2" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4</v>
+      </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>

--- a/請GPT產生初版教材.xlsx
+++ b/請GPT產生初版教材.xlsx
@@ -42,14 +42,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">1. 機器學習主要分成以下幾種常見的類型  ： 
-監督式學習（Supervised Learning） ,非監督式學習（Unsupervised Learning）  ,強化學習（Reinforcement Learning）  
-請簡單說明介紹,及其應用
-2.非監督式學習的三大功能  :分群  , 關聯, 降維
-請簡單說明介紹, 各別常用的演算法, 及更多實際生活中的應用  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">
 在大二資料探勘, 分群課程上課前, 以下四個問題請各以半頁至一頁的篇幅跟同學說明
 一. 什麼是資料Data 
@@ -68,6 +60,15 @@
 四. 公司資料上雲端, 就一定要架私有雲/公有雲嗎? Google 或其他ISP有其他更簡便的方式協助企業資料上雲端嗎?
 如果跟Google申請專屬的企業版 Gmail 與雲端硬碟空間, 其上應該只能上傳file也是不能安裝SQL資料庫, 必須架雲對吧?
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">幫忙產生markdown 格式的教學內容:
+1. 機器學習主要分成以下幾種常見的類型  ： 
+監督式學習（Supervised Learning） ,非監督式學習（Unsupervised Learning）  ,強化學習（Reinforcement Learning）  
+請簡單說明介紹,及其應用
+2.非監督式學習的三大功能  :分群  , 關聯, 降維
+請簡單說明介紹, 各別常用的演算法, 及更多實際生活中的應用  </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -428,7 +429,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -436,7 +437,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
